--- a/EASYCAD.bundle/CONTENTS/48/EASYCADCOMMANDS.xlsx
+++ b/EASYCAD.bundle/CONTENTS/48/EASYCADCOMMANDS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20416"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AUTOLISP\CAD.NET\CAD ONE PROJECT\EASYCAD\EASYCAD\MENU\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AUTOLISP\CAD.NET\INNO SETUP\EASYCAD.bundle\CONTENTS\48\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7C22785-A793-4B52-AACF-40FE07ED722E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3660E6B-08E5-4574-9F3D-1B1573C56908}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" tabRatio="589" firstSheet="3" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" tabRatio="589" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="6" r:id="rId1"/>
@@ -120,9 +120,6 @@
     <t>HM</t>
   </si>
   <si>
-    <t>CFX</t>
-  </si>
-  <si>
     <t>PDS</t>
   </si>
   <si>
@@ -246,9 +243,6 @@
     <t>[HM]..Insert HatchMark For ELE Circuits</t>
   </si>
   <si>
-    <t>[CFX]..Distribution Of Lighting Fixture</t>
-  </si>
-  <si>
     <t>[PDS]..Distribution Of Electrical Fixture</t>
   </si>
   <si>
@@ -334,6 +328,12 @@
   </si>
   <si>
     <t>[ Check Update EASYCAD ]</t>
+  </si>
+  <si>
+    <t>LDS</t>
+  </si>
+  <si>
+    <t>[LDS]..Distribution Of Lighting Fixture</t>
   </si>
 </sst>
 </file>
@@ -697,15 +697,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -713,7 +713,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -721,7 +721,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -741,10 +741,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -764,10 +764,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -787,10 +787,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -810,18 +810,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -849,7 +849,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
@@ -857,7 +857,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -870,26 +870,26 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -909,26 +909,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -941,23 +941,23 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -980,7 +980,7 @@
         <v>22</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -988,12 +988,12 @@
         <v>24</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1001,12 +1001,12 @@
         <v>23</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1014,7 +1014,7 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1022,41 +1022,41 @@
         <v>26</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1128,39 +1128,39 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1180,44 +1180,44 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1240,12 +1240,12 @@
         <v>17</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1253,7 +1253,7 @@
         <v>18</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1261,7 +1261,7 @@
         <v>19</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1269,7 +1269,7 @@
         <v>20</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1277,7 +1277,7 @@
         <v>21</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1297,39 +1297,39 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/EASYCAD.bundle/CONTENTS/48/EASYCADCOMMANDS.xlsx
+++ b/EASYCAD.bundle/CONTENTS/48/EASYCADCOMMANDS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AUTOLISP\CAD.NET\INNO SETUP\EASYCAD.bundle\CONTENTS\48\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AUTOLISP\CAD.NET\CAD ONE PROJECT\EASYCAD\EASYCAD\MENU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3660E6B-08E5-4574-9F3D-1B1573C56908}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F31E722-9213-4688-A58D-F7272890EEEC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" tabRatio="589" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" tabRatio="589" firstSheet="3" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="6" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="103">
   <si>
     <t>ALB</t>
   </si>
@@ -288,9 +288,6 @@
     <t>[MLD]..Adjust Distance Between Mleaders</t>
   </si>
   <si>
-    <t>[QSS]..Count Or Total Length Of Dynamic Blocks</t>
-  </si>
-  <si>
     <t>[ATX]..Align Texts With Each Other</t>
   </si>
   <si>
@@ -334,6 +331,21 @@
   </si>
   <si>
     <t>[LDS]..Distribution Of Lighting Fixture</t>
+  </si>
+  <si>
+    <t>CBE</t>
+  </si>
+  <si>
+    <t>[CBE]..Check Clashes Between Elements</t>
+  </si>
+  <si>
+    <t>[QSS]..Count Or Total Length Of All Blocks</t>
+  </si>
+  <si>
+    <t>CADQSS</t>
+  </si>
+  <si>
+    <t>[CADQSS]..Count Or Total Length Of All Blocks Without Open Files</t>
   </si>
 </sst>
 </file>
@@ -697,10 +709,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -744,7 +756,7 @@
         <v>42</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -754,11 +766,11 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41610008-4AB9-4179-BAD8-F71E0102847B}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
-    <col min="2" max="2" width="54.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="67.85546875" style="2" customWidth="1"/>
     <col min="3" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
@@ -767,7 +779,20 @@
         <v>43</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>83</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -787,10 +812,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -810,18 +835,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1032,10 +1057,10 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1066,7 +1091,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DE302D1-7E0C-4273-96EC-EB5EFC1AE7F7}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -1076,38 +1101,51 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>9</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>48</v>
+        <v>13</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1131,7 +1169,7 @@
         <v>44</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1139,7 +1177,7 @@
         <v>46</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1152,7 +1190,7 @@
         <v>45</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1160,7 +1198,7 @@
         <v>47</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/EASYCAD.bundle/CONTENTS/48/EASYCADCOMMANDS.xlsx
+++ b/EASYCAD.bundle/CONTENTS/48/EASYCADCOMMANDS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AUTOLISP\CAD.NET\CAD ONE PROJECT\EASYCAD\EASYCAD\MENU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C2C2187-57F0-4509-ACC1-D238841D7C0D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFEF697E-8054-45B1-B864-921DCCE67D52}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" tabRatio="589" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" tabRatio="589" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="6" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="105">
   <si>
     <t>ALB</t>
   </si>
@@ -120,9 +120,6 @@
     <t>HM</t>
   </si>
   <si>
-    <t>CFX</t>
-  </si>
-  <si>
     <t>PDS</t>
   </si>
   <si>
@@ -291,9 +288,6 @@
     <t>[MLD]..Adjust Distance Between Mleaders</t>
   </si>
   <si>
-    <t>[QSS]..Count Or Total Length Of Dynamic Blocks</t>
-  </si>
-  <si>
     <t>[ATX]..Align Texts With Each Other</t>
   </si>
   <si>
@@ -333,13 +327,31 @@
     <t>[ Check Update EASYCAD ]</t>
   </si>
   <si>
-    <t>[CFX].. Calculate Lighting Fixture</t>
-  </si>
-  <si>
     <t>LDS</t>
   </si>
   <si>
     <t>[LDS]..Distribution Of Lighting Fixture</t>
+  </si>
+  <si>
+    <t>CBE</t>
+  </si>
+  <si>
+    <t>[CBE]..Check Clashes Between Elements</t>
+  </si>
+  <si>
+    <t>[QSS]..Count Or Total Length Of All Blocks</t>
+  </si>
+  <si>
+    <t>CADQSS</t>
+  </si>
+  <si>
+    <t>[CADQSS]..Count Or Total Length Of All Blocks Without Open Files</t>
+  </si>
+  <si>
+    <t>MLP</t>
+  </si>
+  <si>
+    <t>[MLP]..Mleader Of Layers Of PolyLines</t>
   </si>
 </sst>
 </file>
@@ -703,15 +715,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -719,7 +731,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -727,7 +739,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -747,10 +759,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -760,20 +772,33 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41610008-4AB9-4179-BAD8-F71E0102847B}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
-    <col min="2" max="2" width="54.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="67.85546875" style="2" customWidth="1"/>
     <col min="3" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>84</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -793,10 +818,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -816,18 +841,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -855,7 +880,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
@@ -863,7 +888,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -876,26 +901,26 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -915,26 +940,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -947,23 +972,23 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -973,7 +998,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ED1A648-7769-461A-82D4-55B1253E36E3}">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -986,7 +1011,7 @@
         <v>22</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -994,12 +1019,12 @@
         <v>24</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1007,12 +1032,12 @@
         <v>23</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1020,7 +1045,7 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1028,49 +1053,41 @@
         <v>26</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>99</v>
+        <v>27</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>100</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>70</v>
+        <v>37</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1080,7 +1097,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DE302D1-7E0C-4273-96EC-EB5EFC1AE7F7}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -1090,38 +1107,51 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>9</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>49</v>
+        <v>13</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1142,39 +1172,39 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1184,7 +1214,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B93C5ED7-CD5A-4C74-8E0C-DC8078F1BBEA}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -1194,44 +1224,52 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1254,12 +1292,12 @@
         <v>17</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1267,7 +1305,7 @@
         <v>18</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1275,7 +1313,7 @@
         <v>19</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1283,7 +1321,7 @@
         <v>20</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1291,7 +1329,7 @@
         <v>21</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1311,39 +1349,39 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/EASYCAD.bundle/CONTENTS/48/EASYCADCOMMANDS.xlsx
+++ b/EASYCAD.bundle/CONTENTS/48/EASYCADCOMMANDS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AUTOLISP\CAD.NET\CAD ONE PROJECT\EASYCAD\EASYCAD\MENU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFEF697E-8054-45B1-B864-921DCCE67D52}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0573A2E-F5E8-4574-83C8-3F0AFC343E7F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" tabRatio="589" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" tabRatio="589" firstSheet="7" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="6" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="111">
   <si>
     <t>ALB</t>
   </si>
@@ -351,7 +351,25 @@
     <t>MLP</t>
   </si>
   <si>
-    <t>[MLP]..Mleader Of Layers Of PolyLines</t>
+    <t>[MLP]..Mleader OF Layers Of PolyLines</t>
+  </si>
+  <si>
+    <t>MLPC</t>
+  </si>
+  <si>
+    <t>UMLP</t>
+  </si>
+  <si>
+    <t>UMLPC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[MLPC]..Mleader OF Combined Layers Of PolyLines </t>
+  </si>
+  <si>
+    <t xml:space="preserve">[UMLPC]..Update Mleader OF Combined Layers Of PolyLines </t>
+  </si>
+  <si>
+    <t>[UMLP]..Update Mleader OF Layers Of PolyLines</t>
   </si>
 </sst>
 </file>
@@ -1214,7 +1232,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B93C5ED7-CD5A-4C74-8E0C-DC8078F1BBEA}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -1270,6 +1288,35 @@
       </c>
       <c r="B7" s="2" t="s">
         <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/EASYCAD.bundle/CONTENTS/48/EASYCADCOMMANDS.xlsx
+++ b/EASYCAD.bundle/CONTENTS/48/EASYCADCOMMANDS.xlsx
@@ -8,18 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AUTOLISP\CAD.NET\CAD ONE PROJECT\EASYCAD\EASYCAD\MENU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0573A2E-F5E8-4574-83C8-3F0AFC343E7F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B35253-4B89-4D2F-B7FF-51F904C11070}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" tabRatio="589" firstSheet="7" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" tabRatio="589" firstSheet="7" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="6" r:id="rId1"/>
     <sheet name="Blocks" sheetId="2" r:id="rId2"/>
-    <sheet name="Lines||PolyLines" sheetId="8" r:id="rId3"/>
+    <sheet name="Lines || PolyLines" sheetId="8" r:id="rId3"/>
     <sheet name="Electrical" sheetId="5" r:id="rId4"/>
     <sheet name="Coordination" sheetId="3" r:id="rId5"/>
-    <sheet name="Text||MText" sheetId="12" r:id="rId6"/>
-    <sheet name="Leaders||Mleaders" sheetId="9" r:id="rId7"/>
+    <sheet name="Text || MText" sheetId="12" r:id="rId6"/>
+    <sheet name="Leaders || Mleaders" sheetId="9" r:id="rId7"/>
     <sheet name="Dimentions" sheetId="4" r:id="rId8"/>
     <sheet name="Layout" sheetId="7" r:id="rId9"/>
     <sheet name="Points" sheetId="10" r:id="rId10"/>
@@ -354,22 +354,22 @@
     <t>[MLP]..Mleader OF Layers Of PolyLines</t>
   </si>
   <si>
-    <t>MLPC</t>
-  </si>
-  <si>
-    <t>UMLP</t>
-  </si>
-  <si>
-    <t>UMLPC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[MLPC]..Mleader OF Combined Layers Of PolyLines </t>
-  </si>
-  <si>
-    <t xml:space="preserve">[UMLPC]..Update Mleader OF Combined Layers Of PolyLines </t>
-  </si>
-  <si>
-    <t>[UMLP]..Update Mleader OF Layers Of PolyLines</t>
+    <t>MPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[MPL]..Mleader OF Combined Layers Of PolyLines </t>
+  </si>
+  <si>
+    <t>UMP</t>
+  </si>
+  <si>
+    <t>UMC</t>
+  </si>
+  <si>
+    <t>[UMP]..Update Mleader OF Layers Of PolyLines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[UMC]..Update Mleader OF Combined Layers Of PolyLines </t>
   </si>
 </sst>
 </file>
@@ -1295,7 +1295,7 @@
         <v>105</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1305,18 +1305,18 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/EASYCAD.bundle/CONTENTS/48/EASYCADCOMMANDS.xlsx
+++ b/EASYCAD.bundle/CONTENTS/48/EASYCADCOMMANDS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AUTOLISP\CAD.NET\CAD ONE PROJECT\EASYCAD\EASYCAD\MENU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B35253-4B89-4D2F-B7FF-51F904C11070}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0769AA8D-CE78-47DC-BD69-F8FC68D29913}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" tabRatio="589" firstSheet="7" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" tabRatio="589" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="6" r:id="rId1"/>
@@ -354,22 +354,22 @@
     <t>[MLP]..Mleader OF Layers Of PolyLines</t>
   </si>
   <si>
-    <t>MPL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[MPL]..Mleader OF Combined Layers Of PolyLines </t>
-  </si>
-  <si>
-    <t>UMP</t>
-  </si>
-  <si>
-    <t>UMC</t>
-  </si>
-  <si>
-    <t>[UMP]..Update Mleader OF Layers Of PolyLines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[UMC]..Update Mleader OF Combined Layers Of PolyLines </t>
+    <t>MLPC</t>
+  </si>
+  <si>
+    <t>UMLP</t>
+  </si>
+  <si>
+    <t>UMLPC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[MLPC]..Mleader OF Combined Layers Of PolyLines </t>
+  </si>
+  <si>
+    <t>[UMLP]..Update Mleader OF Layers Of PolyLines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[UMLPC]..Update Mleader OF Combined Layers Of PolyLines </t>
   </si>
 </sst>
 </file>
@@ -1295,7 +1295,7 @@
         <v>105</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1305,7 +1305,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>109</v>
@@ -1313,7 +1313,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>110</v>
